--- a/update-tests/issues_list.xlsx
+++ b/update-tests/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C507"/>
+  <dimension ref="A1:C500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.ncbi.nlm.nih.gov/bioproject/PRJNA1269471 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: http://www.ncbi.nlm.nih.gov/bioproject/1049344 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaM3BtUW5KQ2ZtLW8/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaSkItaW5ocTY4UjQ/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaM3BtUW5KQ2ZtLW8/view?usp=sharing returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaSkItaW5ocTY4UjQ/view?usp=sharing returned status_code=401</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.ncbi.nlm.nih.gov/bioproject/PRJNA1456220 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.ncbi.nlm.nih.gov/bioproject/PRJNA865652/ returned status_code=500</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/file/d/12FLUjCgtid772zCGwf322CIGkoNbReug/view returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/file/d/12FLUjCgtid772zCGwf322CIGkoNbReug/view returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3209,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3299,12 +3299,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.ncbi.nlm.nih.gov/bioproject/1269473 returned status_code=404</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/file/d/1w7TLX1RIP6F6S_inRKU3x-A27srXzFSa/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.ncbi.nlm.nih.gov/bioproject/?term=PRJNA1195080 returned status_code=500</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.ncbi.nlm.nih.gov/bioproject/1232168/ returned status_code=500</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/file/d/1w7TLX1RIP6F6S_inRKU3x-A27srXzFSa/view?usp=sharing returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -4919,12 +4919,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5129,12 +5129,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -5504,12 +5504,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5549,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5864,12 +5864,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Janusson, Carly</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Janusson, Carly</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -6059,12 +6059,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: Pontier, Ondine</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6149,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -6164,12 +6164,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Pontier, Ondine</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6269,12 +6269,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Opie, Rumer</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Obrist, Debora S</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Fitzpatrick, O. T.</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Opie, Rumer</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Organization missing ROR: University of Victoria</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Obrist, Debora S</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Fitzpatrick, O. T.</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Johnson, Brett</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Johnson, Brett</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of Victoria</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: van Meerveld, H. J.</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Timmer, Brian</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Organization missing ROR: University Of Victoria</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: van Meerveld, H. J.</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Savage, Rosie</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Savage, Rosie</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Johnson, Brett</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Timmer, Brian</t>
+          <t>Contact missing ORCID: Gan, Julian</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University Of Victoria</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Organization missing ROR: University of Toronto</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Johnson, Brett</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gan, Julian</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of Toronto</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -7334,12 +7334,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -7544,12 +7544,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7604,12 +7604,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -7634,12 +7634,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Burt, Jenn</t>
         </is>
       </c>
     </row>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Burt, Jenn</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7754,12 +7754,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Johnson, Brett T.</t>
         </is>
       </c>
     </row>
@@ -7769,12 +7769,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Hunt, Brian P.V.</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -7799,12 +7799,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Gan, Julian C.L.</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -7829,12 +7829,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Whalen, Matt</t>
         </is>
       </c>
     </row>
@@ -7844,12 +7844,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Johnson, Brett T.</t>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P.V.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7904,117 +7904,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="n">
-        <v>499</v>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gan, Julian C.L.</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="n">
-        <v>500</v>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Whalen, Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="n">
-        <v>501</v>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="n">
-        <v>502</v>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
           <t>Contact missing ORCID: Hare, Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="n">
-        <v>503</v>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="n">
-        <v>504</v>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="n">
-        <v>505</v>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>

--- a/update-tests/issues_list.xlsx
+++ b/update-tests/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C500"/>
+  <dimension ref="A1:C475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,12 +464,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -479,12 +479,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaM3BtUW5KQ2ZtLW8/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaSkItaW5ocTY4UjQ/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaM3BtUW5KQ2ZtLW8/view?usp=sharing returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaSkItaW5ocTY4UjQ/view?usp=sharing returned status_code=401</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2909,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/file/d/12FLUjCgtid772zCGwf322CIGkoNbReug/view returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/file/d/12FLUjCgtid772zCGwf322CIGkoNbReug/view returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4349,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/file/d/1w7TLX1RIP6F6S_inRKU3x-A27srXzFSa/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4439,12 +4439,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4454,12 +4454,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/file/d/1w7TLX1RIP6F6S_inRKU3x-A27srXzFSa/view?usp=sharing returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5129,12 +5129,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -5429,12 +5429,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5549,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Janusson, Carly</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Pontier, Ondine</t>
         </is>
       </c>
     </row>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -5864,12 +5864,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Janusson, Carly</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Opie, Rumer</t>
         </is>
       </c>
     </row>
@@ -6059,12 +6059,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Pontier, Ondine</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Obrist, Debora S</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Fitzpatrick, O. T.</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6149,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Organization missing ROR: University of Victoria</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Johnson, Brett</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -6269,12 +6269,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Opie, Rumer</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Obrist, Debora S</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Fitzpatrick, O. T.</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of Victoria</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Johnson, Brett</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Contact missing ORCID: van Meerveld, H. J.</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Contact missing ORCID: Timmer, Brian</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Organization missing ROR: University Of Victoria</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: Savage, Rosie</t>
         </is>
       </c>
     </row>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -6659,12 +6659,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: van Meerveld, H. J.</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Timmer, Brian</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University Of Victoria</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Savage, Rosie</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Johnson, Brett</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gan, Julian</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of Toronto</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>29f9a024-3b5f-46d1-a3b1-8c333eeaa89f</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Burt, Jenn</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Whalen, Matt</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7529,385 +7529,10 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="n">
-        <v>474</v>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="n">
-        <v>475</v>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="n">
-        <v>476</v>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="n">
-        <v>477</v>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="n">
-        <v>478</v>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="n">
-        <v>479</v>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="n">
-        <v>480</v>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="n">
-        <v>481</v>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="n">
-        <v>482</v>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="n">
-        <v>483</v>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="n">
-        <v>484</v>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Burt, Jenn</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="n">
-        <v>485</v>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="n">
-        <v>486</v>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="n">
-        <v>487</v>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="n">
-        <v>488</v>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Johnson, Brett T.</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="n">
-        <v>489</v>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hunt, Brian P.V.</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="n">
-        <v>490</v>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>Organization missing ROR: University of British Columbia</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="n">
-        <v>491</v>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>1919ea31-8ac0-4bbb-aa2e-e9121996e41e</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gan, Julian C.L.</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="n">
-        <v>492</v>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="n">
-        <v>493</v>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Whalen, Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="n">
-        <v>494</v>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="n">
-        <v>495</v>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="n">
-        <v>496</v>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="n">
-        <v>497</v>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="n">
-        <v>498</v>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
         <is>
           <t>Contact missing ORCID: Hare, Alex</t>
         </is>

--- a/update-tests/issues_list.xlsx
+++ b/update-tests/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C475"/>
+  <dimension ref="A1:C480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,12 +464,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -479,12 +479,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaM3BtUW5KQ2ZtLW8/view?usp=sharing returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaSkItaW5ocTY4UjQ/view?usp=sharing returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaM3BtUW5KQ2ZtLW8/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaSkItaW5ocTY4UjQ/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/file/d/12FLUjCgtid772zCGwf322CIGkoNbReug/view returned status_code=401</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/file/d/12FLUjCgtid772zCGwf322CIGkoNbReug/view returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3299,12 +3299,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/file/d/1w7TLX1RIP6F6S_inRKU3x-A27srXzFSa/view?usp=sharing returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/file/d/1w7TLX1RIP6F6S_inRKU3x-A27srXzFSa/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5429,12 +5429,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5549,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Janusson, Carly</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Janusson, Carly</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Pontier, Ondine</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -5864,12 +5864,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: Pontier, Ondine</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Opie, Rumer</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -6059,12 +6059,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Obrist, Debora S</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Fitzpatrick, O. T.</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Opie, Rumer</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6149,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6164,12 +6164,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Obrist, Debora S</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of Victoria</t>
+          <t>Contact missing ORCID: Fitzpatrick, O. T.</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Johnson, Brett</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Organization missing ROR: University of Victoria</t>
         </is>
       </c>
     </row>
@@ -6269,12 +6269,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Contact missing ORCID: Johnson, Brett</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: van Meerveld, H. J.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: van Meerveld, H. J.</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Timmer, Brian</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University Of Victoria</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Savage, Rosie</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -6659,12 +6659,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Timmer, Brian</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Organization missing ROR: University Of Victoria</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Savage, Rosie</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -7334,12 +7334,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Burt, Jenn</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Burt, Jenn</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Whalen, Matt</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,87 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Whalen, Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>474</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>475</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
           <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr">
+      <c r="C477" t="inlineStr">
         <is>
           <t>Contact missing ORCID: Hare, Alex</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>476</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>477</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>478</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>

--- a/update-tests/issues_list.xlsx
+++ b/update-tests/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C480"/>
+  <dimension ref="A1:C461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaM3BtUW5KQ2ZtLW8/view?usp=sharing returned status_code=401</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaSkItaW5ocTY4UjQ/view?usp=sharing returned status_code=401</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaM3BtUW5KQ2ZtLW8/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/a/hakai.org/file/d/0Byed_WX-ZNMaSkItaW5ocTY4UjQ/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/file/d/12FLUjCgtid772zCGwf322CIGkoNbReug/view returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/file/d/12FLUjCgtid772zCGwf322CIGkoNbReug/view returned status_code=401</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3209,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3299,12 +3299,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://catalogue.hakai.org/erddap/tabledap/HakaiBIOOSBuoyResearch.html returned status_code=502</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Invalid Resource URL: https://drive.google.com/file/d/1w7TLX1RIP6F6S_inRKU3x-A27srXzFSa/view?usp=sharing returned status_code=401</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4439,12 +4439,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/file/d/1w7TLX1RIP6F6S_inRKU3x-A27srXzFSa/view?usp=sharing returned status_code=401</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -5429,12 +5429,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Janusson, Carly</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5549,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Janusson, Carly</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Pontier, Ondine</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -5864,12 +5864,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Pontier, Ondine</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>782fef82-e6e7-451d-a7ac-39d08129c1d3</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Opie, Rumer</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Obrist, Debora S</t>
         </is>
       </c>
     </row>
@@ -6059,12 +6059,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Fitzpatrick, O. T.</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Opie, Rumer</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6149,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -6164,12 +6164,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Obrist, Debora S</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Fitzpatrick, O. T.</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of Victoria</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -6269,12 +6269,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>d7ca7d43-b0fb-4dfc-beb1-7033388011a0</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Johnson, Brett</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: van Meerveld, H. J.</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Savage, Rosie</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: van Meerveld, H. J.</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -6659,12 +6659,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Timmer, Brian</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University Of Victoria</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Savage, Rosie</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Burt, Jenn</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Whalen, Matt</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -7319,297 +7319,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="n">
-        <v>460</v>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="n">
-        <v>461</v>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="n">
-        <v>462</v>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="n">
-        <v>463</v>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="n">
-        <v>464</v>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Burt, Jenn</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="n">
-        <v>465</v>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="n">
-        <v>466</v>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="n">
-        <v>467</v>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="n">
-        <v>468</v>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="n">
-        <v>469</v>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="n">
-        <v>470</v>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="n">
-        <v>471</v>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="n">
-        <v>472</v>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
           <t>Contact missing ORCID: Hare, Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="n">
-        <v>473</v>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Whalen, Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="n">
-        <v>474</v>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="n">
-        <v>475</v>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="n">
-        <v>476</v>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="n">
-        <v>477</v>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="n">
-        <v>478</v>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
